--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/24.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/24.xlsx
@@ -426,13 +426,13 @@
         <v>-20.20191339796767</v>
       </c>
       <c r="E2">
-        <v>-11.62239401602968</v>
+        <v>-10.20547072682169</v>
       </c>
       <c r="F2">
-        <v>-1.81529425204236</v>
+        <v>-2.07221252788044</v>
       </c>
       <c r="G2">
-        <v>-11.74386350213434</v>
+        <v>-11.60516157567549</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.60164064664651</v>
       </c>
       <c r="E3">
-        <v>-12.0663746646897</v>
+        <v>-10.73285228128097</v>
       </c>
       <c r="F3">
-        <v>-1.598087402033925</v>
+        <v>-1.757399506744598</v>
       </c>
       <c r="G3">
-        <v>-11.27315358463306</v>
+        <v>-11.472306072639</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.90469668412962</v>
       </c>
       <c r="E4">
-        <v>-13.34965362898332</v>
+        <v>-11.54430501024141</v>
       </c>
       <c r="F4">
-        <v>-1.917256406290183</v>
+        <v>-2.167970514204529</v>
       </c>
       <c r="G4">
-        <v>-10.3081626653909</v>
+        <v>-9.968149775234517</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.2190031536826</v>
       </c>
       <c r="E5">
-        <v>-13.94997984275816</v>
+        <v>-14.03827150048571</v>
       </c>
       <c r="F5">
-        <v>-1.528993480355132</v>
+        <v>-2.17783937761659</v>
       </c>
       <c r="G5">
-        <v>-9.982302357414902</v>
+        <v>-10.52764521355351</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.54251326941716</v>
       </c>
       <c r="E6">
-        <v>-14.73377718095376</v>
+        <v>-14.06797376150202</v>
       </c>
       <c r="F6">
-        <v>-1.706918088837008</v>
+        <v>-1.987197610633735</v>
       </c>
       <c r="G6">
-        <v>-9.717435540454431</v>
+        <v>-9.699091807621329</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.90999134417688</v>
       </c>
       <c r="E7">
-        <v>-14.16847418515425</v>
+        <v>-14.22450499405115</v>
       </c>
       <c r="F7">
-        <v>-1.749245004986</v>
+        <v>-2.0480570534052</v>
       </c>
       <c r="G7">
-        <v>-8.906782254253097</v>
+        <v>-9.544552231302612</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.32698836818899</v>
       </c>
       <c r="E8">
-        <v>-16.19113068610224</v>
+        <v>-15.6918211420165</v>
       </c>
       <c r="F8">
-        <v>-1.57575318936144</v>
+        <v>-2.19095879742009</v>
       </c>
       <c r="G8">
-        <v>-9.57603882992662</v>
+        <v>-8.655869386740655</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.788800794315</v>
       </c>
       <c r="E9">
-        <v>-16.96245207840671</v>
+        <v>-15.91332691962769</v>
       </c>
       <c r="F9">
-        <v>-1.50774173067585</v>
+        <v>-2.10177160693916</v>
       </c>
       <c r="G9">
-        <v>-8.611051221230001</v>
+        <v>-7.958168603793712</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.29683262825826</v>
       </c>
       <c r="E10">
-        <v>-16.22769358524017</v>
+        <v>-17.13998637340341</v>
       </c>
       <c r="F10">
-        <v>-1.541190391462889</v>
+        <v>-2.216005106472765</v>
       </c>
       <c r="G10">
-        <v>-7.785129699001547</v>
+        <v>-7.906153312280683</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.82074424939748</v>
       </c>
       <c r="E11">
-        <v>-17.48453984675102</v>
+        <v>-16.78478645766377</v>
       </c>
       <c r="F11">
-        <v>-1.177104320032938</v>
+        <v>-1.925051406805976</v>
       </c>
       <c r="G11">
-        <v>-7.484062066569146</v>
+        <v>-7.404320956164721</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.35332368103094</v>
       </c>
       <c r="E12">
-        <v>-17.73478332041488</v>
+        <v>-15.48049084550055</v>
       </c>
       <c r="F12">
-        <v>-1.463553168223259</v>
+        <v>-1.53466156382649</v>
       </c>
       <c r="G12">
-        <v>-7.89939979938057</v>
+        <v>-6.211978322013114</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.85670545103099</v>
       </c>
       <c r="E13">
-        <v>-19.07255341244281</v>
+        <v>-18.53570734730749</v>
       </c>
       <c r="F13">
-        <v>-1.513017846933137</v>
+        <v>-2.115945774882343</v>
       </c>
       <c r="G13">
-        <v>-6.01376933948587</v>
+        <v>-5.464837851982696</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.32795419848383</v>
       </c>
       <c r="E14">
-        <v>-20.23499910478976</v>
+        <v>-20.12675499058442</v>
       </c>
       <c r="F14">
-        <v>-1.047600728062665</v>
+        <v>-1.744412326385037</v>
       </c>
       <c r="G14">
-        <v>-6.023876435017264</v>
+        <v>-5.993551837877541</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.75692291479013</v>
       </c>
       <c r="E15">
-        <v>-20.38466969921728</v>
+        <v>-19.58042630087705</v>
       </c>
       <c r="F15">
-        <v>-0.8570389382285407</v>
+        <v>-1.526240999474099</v>
       </c>
       <c r="G15">
-        <v>-5.350597546513526</v>
+        <v>-4.821638580248775</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.14729544586922</v>
       </c>
       <c r="E16">
-        <v>-21.76066464034395</v>
+        <v>-22.57949878193689</v>
       </c>
       <c r="F16">
-        <v>-0.6385199878691635</v>
+        <v>-1.260504649098852</v>
       </c>
       <c r="G16">
-        <v>-5.248401005716224</v>
+        <v>-5.10452138603396</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.52020686617086</v>
       </c>
       <c r="E17">
-        <v>-21.95385386998517</v>
+        <v>-21.90231077882987</v>
       </c>
       <c r="F17">
-        <v>-0.8126096524768025</v>
+        <v>-1.028064131889804</v>
       </c>
       <c r="G17">
-        <v>-4.87553757217365</v>
+        <v>-4.36824612646343</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.88503442188863</v>
       </c>
       <c r="E18">
-        <v>-22.8643035692273</v>
+        <v>-23.21721660559307</v>
       </c>
       <c r="F18">
-        <v>-0.2800148960852203</v>
+        <v>-0.8249411785873717</v>
       </c>
       <c r="G18">
-        <v>-4.738265801387771</v>
+        <v>-3.660600464716517</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.27638653324789</v>
       </c>
       <c r="E19">
-        <v>-23.82001083770208</v>
+        <v>-22.54636393762277</v>
       </c>
       <c r="F19">
-        <v>-0.3303799116080257</v>
+        <v>-0.495063154930912</v>
       </c>
       <c r="G19">
-        <v>-4.161333719713441</v>
+        <v>-3.816043819967456</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.704064024969615</v>
       </c>
       <c r="E20">
-        <v>-25.10640086363898</v>
+        <v>-24.31649008553302</v>
       </c>
       <c r="F20">
-        <v>0.3060338942172317</v>
+        <v>-0.2793133143646807</v>
       </c>
       <c r="G20">
-        <v>-4.197309418088701</v>
+        <v>-3.411776551439355</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.198649877699555</v>
       </c>
       <c r="E21">
-        <v>-25.37141169104185</v>
+        <v>-25.45011656929517</v>
       </c>
       <c r="F21">
-        <v>0.247081233367956</v>
+        <v>-0.4265615392644942</v>
       </c>
       <c r="G21">
-        <v>-4.918256851812405</v>
+        <v>-3.534342878939793</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.768193227374582</v>
       </c>
       <c r="E22">
-        <v>-26.07446180920669</v>
+        <v>-26.20153078986191</v>
       </c>
       <c r="F22">
-        <v>0.5500544690799727</v>
+        <v>-0.2427851374250698</v>
       </c>
       <c r="G22">
-        <v>-3.940434258060032</v>
+        <v>-2.924480800786333</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.423986515390215</v>
       </c>
       <c r="E23">
-        <v>-26.06164622776498</v>
+        <v>-26.70061391024726</v>
       </c>
       <c r="F23">
-        <v>0.9113231276863577</v>
+        <v>-0.0633259179111334</v>
       </c>
       <c r="G23">
-        <v>-4.509864643542373</v>
+        <v>-3.351170394251918</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.171901421722334</v>
       </c>
       <c r="E24">
-        <v>-27.85355886412613</v>
+        <v>-26.44099196691351</v>
       </c>
       <c r="F24">
-        <v>1.014531658489631</v>
+        <v>0.09134592846730252</v>
       </c>
       <c r="G24">
-        <v>-4.696470163954471</v>
+        <v>-2.863758774505021</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.000437818298073</v>
       </c>
       <c r="E25">
-        <v>-27.71494680322535</v>
+        <v>-27.18946720784929</v>
       </c>
       <c r="F25">
-        <v>0.782792723001123</v>
+        <v>0.09723335520794867</v>
       </c>
       <c r="G25">
-        <v>-3.951954956536696</v>
+        <v>-3.337527636084581</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.908314984287415</v>
       </c>
       <c r="E26">
-        <v>-26.89322802368952</v>
+        <v>-27.80364602361359</v>
       </c>
       <c r="F26">
-        <v>0.8997779115628041</v>
+        <v>0.1846341254162632</v>
       </c>
       <c r="G26">
-        <v>-4.065026639430503</v>
+        <v>-2.962866576314182</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.870098497247402</v>
       </c>
       <c r="E27">
-        <v>-27.87090744804951</v>
+        <v>-25.24499028216972</v>
       </c>
       <c r="F27">
-        <v>0.7950886157285949</v>
+        <v>0.7596737840475379</v>
       </c>
       <c r="G27">
-        <v>-3.968686453692172</v>
+        <v>-3.4812516601265</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.877145366265442</v>
       </c>
       <c r="E28">
-        <v>-26.32997189814147</v>
+        <v>-27.8066076456146</v>
       </c>
       <c r="F28">
-        <v>0.9824331069955042</v>
+        <v>0.384247586410082</v>
       </c>
       <c r="G28">
-        <v>-3.817288585090223</v>
+        <v>-3.792287345177646</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.902288306599623</v>
       </c>
       <c r="E29">
-        <v>-26.8991240968475</v>
+        <v>-27.27811208654943</v>
       </c>
       <c r="F29">
-        <v>0.8383649635738932</v>
+        <v>-0.1334049046693289</v>
       </c>
       <c r="G29">
-        <v>-4.341814730877888</v>
+        <v>-3.078563521820632</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.932337856279873</v>
       </c>
       <c r="E30">
-        <v>-26.77222719820456</v>
+        <v>-26.48306601891878</v>
       </c>
       <c r="F30">
-        <v>0.8196534781829761</v>
+        <v>0.3760336956796553</v>
       </c>
       <c r="G30">
-        <v>-4.315833569485688</v>
+        <v>-3.088366047162414</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.953299101939509</v>
       </c>
       <c r="E31">
-        <v>-27.0881652442977</v>
+        <v>-26.19899484441762</v>
       </c>
       <c r="F31">
-        <v>0.9837254110225029</v>
+        <v>0.4301584290457139</v>
       </c>
       <c r="G31">
-        <v>-4.09806588391243</v>
+        <v>-3.853618511838184</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.95110499258069</v>
       </c>
       <c r="E32">
-        <v>-26.3742694308845</v>
+        <v>-26.09822724079894</v>
       </c>
       <c r="F32">
-        <v>0.8849544241942908</v>
+        <v>0.344761838673388</v>
       </c>
       <c r="G32">
-        <v>-4.711301407970407</v>
+        <v>-2.924609912062365</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.928297100650029</v>
       </c>
       <c r="E33">
-        <v>-25.6343394204012</v>
+        <v>-25.75590630513711</v>
       </c>
       <c r="F33">
-        <v>0.8886793005074044</v>
+        <v>0.1080548177281464</v>
       </c>
       <c r="G33">
-        <v>-4.145267642211358</v>
+        <v>-3.229640267505272</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.877687798397238</v>
       </c>
       <c r="E34">
-        <v>-25.00056589760571</v>
+        <v>-26.1800884654356</v>
       </c>
       <c r="F34">
-        <v>0.630482973995565</v>
+        <v>0.253155537406624</v>
       </c>
       <c r="G34">
-        <v>-4.371258722904166</v>
+        <v>-3.081632397535536</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.812209340187013</v>
       </c>
       <c r="E35">
-        <v>-25.63924375775151</v>
+        <v>-25.10630123721081</v>
       </c>
       <c r="F35">
-        <v>0.5031807332477536</v>
+        <v>0.1445053930779007</v>
       </c>
       <c r="G35">
-        <v>-3.546658108345881</v>
+        <v>-2.865837797103683</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.732388803796781</v>
       </c>
       <c r="E36">
-        <v>-24.35751353156851</v>
+        <v>-25.22073577538464</v>
       </c>
       <c r="F36">
-        <v>0.7948209694288856</v>
+        <v>0.09208314357093958</v>
       </c>
       <c r="G36">
-        <v>-3.728294499903534</v>
+        <v>-3.673504971228596</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.652939487750378</v>
       </c>
       <c r="E37">
-        <v>-24.43682975381285</v>
+        <v>-24.41147482784391</v>
       </c>
       <c r="F37">
-        <v>0.6305257340552819</v>
+        <v>-0.02558066297550732</v>
       </c>
       <c r="G37">
-        <v>-3.018059991544912</v>
+        <v>-3.020665390884318</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.581497580338446</v>
       </c>
       <c r="E38">
-        <v>-23.99273589330264</v>
+        <v>-24.7223681538925</v>
       </c>
       <c r="F38">
-        <v>0.6389732214082359</v>
+        <v>0.2056989977975233</v>
       </c>
       <c r="G38">
-        <v>-3.452565783028716</v>
+        <v>-3.077368414880955</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.523897136985346</v>
       </c>
       <c r="E39">
-        <v>-22.69850255038446</v>
+        <v>-24.11376841810565</v>
       </c>
       <c r="F39">
-        <v>0.4459836104057425</v>
+        <v>-0.2811060694609581</v>
       </c>
       <c r="G39">
-        <v>-3.193273924756379</v>
+        <v>-2.387228917945708</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.49287006602953</v>
       </c>
       <c r="E40">
-        <v>-22.97055515486927</v>
+        <v>-24.06224796932039</v>
       </c>
       <c r="F40">
-        <v>0.5419601481461617</v>
+        <v>0.0167114116433454</v>
       </c>
       <c r="G40">
-        <v>-3.576092168735542</v>
+        <v>-2.90359787952461</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.486614829777673</v>
       </c>
       <c r="E41">
-        <v>-23.73802281579321</v>
+        <v>-22.77220799333331</v>
       </c>
       <c r="F41">
-        <v>0.6082477429427952</v>
+        <v>0.2155243092969096</v>
       </c>
       <c r="G41">
-        <v>-3.086512141660422</v>
+        <v>-1.503190768775348</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.518193155743202</v>
       </c>
       <c r="E42">
-        <v>-21.32555527226496</v>
+        <v>-22.27804732419429</v>
       </c>
       <c r="F42">
-        <v>0.4324682641233823</v>
+        <v>0.380063435381491</v>
       </c>
       <c r="G42">
-        <v>-2.42074488098529</v>
+        <v>-1.926142756327096</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.581714372844766</v>
       </c>
       <c r="E43">
-        <v>-21.6198879688675</v>
+        <v>-22.1388963748866</v>
       </c>
       <c r="F43">
-        <v>0.4617763257945047</v>
+        <v>-0.03034999333985322</v>
       </c>
       <c r="G43">
-        <v>-3.117760381005603</v>
+        <v>-2.728791143414474</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.685213770657571</v>
       </c>
       <c r="E44">
-        <v>-20.02551189719494</v>
+        <v>-21.02349699900533</v>
       </c>
       <c r="F44">
-        <v>0.7551918963068442</v>
+        <v>0.03222064367324391</v>
       </c>
       <c r="G44">
-        <v>-3.025310086275915</v>
+        <v>-2.330661626316182</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.825254140936478</v>
       </c>
       <c r="E45">
-        <v>-20.51459161849734</v>
+        <v>-20.35543387102376</v>
       </c>
       <c r="F45">
-        <v>0.4201446565423902</v>
+        <v>0.1768272471061044</v>
       </c>
       <c r="G45">
-        <v>-3.112629035419732</v>
+        <v>-3.26144798904659</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.002338126872006</v>
       </c>
       <c r="E46">
-        <v>-20.54477842623247</v>
+        <v>-20.08202725281066</v>
       </c>
       <c r="F46">
-        <v>0.3292470636727854</v>
+        <v>-0.3455708187489208</v>
       </c>
       <c r="G46">
-        <v>-3.18840742281365</v>
+        <v>-3.407284141142565</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.220977524233112</v>
       </c>
       <c r="E47">
-        <v>-19.13689397114379</v>
+        <v>-20.40216319430891</v>
       </c>
       <c r="F47">
-        <v>0.515647666214093</v>
+        <v>-0.04160697498679682</v>
       </c>
       <c r="G47">
-        <v>-3.329771027886069</v>
+        <v>-2.433291848579128</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.471689078124728</v>
       </c>
       <c r="E48">
-        <v>-19.55572347516521</v>
+        <v>-19.34187534710099</v>
       </c>
       <c r="F48">
-        <v>0.6671726889385506</v>
+        <v>0.1148932598710139</v>
       </c>
       <c r="G48">
-        <v>-3.041468859053098</v>
+        <v>-2.316187921218488</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.761333025869185</v>
       </c>
       <c r="E49">
-        <v>-18.4374711606591</v>
+        <v>-19.92729382444257</v>
       </c>
       <c r="F49">
-        <v>0.6660656785036585</v>
+        <v>-0.02102434105678803</v>
       </c>
       <c r="G49">
-        <v>-3.753305671452728</v>
+        <v>-3.442210396581876</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.076000836381009</v>
       </c>
       <c r="E50">
-        <v>-18.07886130399169</v>
+        <v>-17.7908775279479</v>
       </c>
       <c r="F50">
-        <v>0.6299270932192458</v>
+        <v>0.1196586309705712</v>
       </c>
       <c r="G50">
-        <v>-3.244680075890181</v>
+        <v>-4.040737166808871</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.419107345110659</v>
       </c>
       <c r="E51">
-        <v>-17.5373056258884</v>
+        <v>-17.82880802623615</v>
       </c>
       <c r="F51">
-        <v>0.3814951055290483</v>
+        <v>0.2882045330212144</v>
       </c>
       <c r="G51">
-        <v>-3.626935527127668</v>
+        <v>-3.54166580567266</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.777069460957522</v>
       </c>
       <c r="E52">
-        <v>-16.99988897302812</v>
+        <v>-17.36168687539693</v>
       </c>
       <c r="F52">
-        <v>0.3539782152482878</v>
+        <v>0.21409343100231</v>
       </c>
       <c r="G52">
-        <v>-3.874855661472609</v>
+        <v>-3.190059385037746</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.14646481147348</v>
       </c>
       <c r="E53">
-        <v>-17.7104699434677</v>
+        <v>-18.29297661202236</v>
       </c>
       <c r="F53">
-        <v>0.3539109077468817</v>
+        <v>0.02095257608489224</v>
       </c>
       <c r="G53">
-        <v>-4.008330236524944</v>
+        <v>-2.887743676937041</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.52242420168088</v>
       </c>
       <c r="E54">
-        <v>-16.3698197419709</v>
+        <v>-16.30017181173293</v>
       </c>
       <c r="F54">
-        <v>0.2688659000877833</v>
+        <v>-0.1278255087292358</v>
       </c>
       <c r="G54">
-        <v>-3.953150063476373</v>
+        <v>-3.669085392933669</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.89081138463789</v>
       </c>
       <c r="E55">
-        <v>-16.20795396704073</v>
+        <v>-15.54679676192086</v>
       </c>
       <c r="F55">
-        <v>0.4741680327298607</v>
+        <v>-0.1238567417051445</v>
       </c>
       <c r="G55">
-        <v>-4.43824430134578</v>
+        <v>-3.657673942459801</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.25703306258121</v>
       </c>
       <c r="E56">
-        <v>-15.49726431322496</v>
+        <v>-16.65983227437012</v>
       </c>
       <c r="F56">
-        <v>0.2729558206144057</v>
+        <v>-0.1605670448250309</v>
       </c>
       <c r="G56">
-        <v>-4.121332397962427</v>
+        <v>-4.513108978170858</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.6055757308275</v>
       </c>
       <c r="E57">
-        <v>-15.16955223471188</v>
+        <v>-16.293130034651</v>
       </c>
       <c r="F57">
-        <v>0.3681017046021768</v>
+        <v>0.1513272063086561</v>
       </c>
       <c r="G57">
-        <v>-4.611001809767107</v>
+        <v>-3.574284610871099</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.94438642581031</v>
       </c>
       <c r="E58">
-        <v>-14.42790140410567</v>
+        <v>-15.51444534361006</v>
       </c>
       <c r="F58">
-        <v>0.4560425185276562</v>
+        <v>-0.1985229326474104</v>
       </c>
       <c r="G58">
-        <v>-4.509589868262613</v>
+        <v>-4.946658021993813</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.26165222594113</v>
       </c>
       <c r="E59">
-        <v>-14.64408622475784</v>
+        <v>-14.70920568098814</v>
       </c>
       <c r="F59">
-        <v>0.6705586521857603</v>
+        <v>-0.07072024083032018</v>
       </c>
       <c r="G59">
-        <v>-5.32577838660561</v>
+        <v>-5.855336561612968</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.56303648174153</v>
       </c>
       <c r="E60">
-        <v>-14.07226675486129</v>
+        <v>-14.52082569074306</v>
       </c>
       <c r="F60">
-        <v>0.2577633297675951</v>
+        <v>-0.03455789995717583</v>
       </c>
       <c r="G60">
-        <v>-5.485485724511131</v>
+        <v>-5.231874762384183</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.84594225788157</v>
       </c>
       <c r="E61">
-        <v>-14.54714065320164</v>
+        <v>-14.35371594291201</v>
       </c>
       <c r="F61">
-        <v>0.2491733088822515</v>
+        <v>-0.2247910708138468</v>
       </c>
       <c r="G61">
-        <v>-5.306113746102339</v>
+        <v>-4.884949453141798</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.10745545244302</v>
       </c>
       <c r="E62">
-        <v>-14.02052441084965</v>
+        <v>-14.57308428079158</v>
       </c>
       <c r="F62">
-        <v>0.4746581897106892</v>
+        <v>0.04018272516311572</v>
       </c>
       <c r="G62">
-        <v>-4.924083411961522</v>
+        <v>-5.001510451033997</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.35648533414541</v>
       </c>
       <c r="E63">
-        <v>-13.53388553703738</v>
+        <v>-14.13844587400939</v>
       </c>
       <c r="F63">
-        <v>0.3598125878407668</v>
+        <v>0.1854885347576427</v>
       </c>
       <c r="G63">
-        <v>-5.12323258942192</v>
+        <v>-6.328423450811439</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.58200284583369</v>
       </c>
       <c r="E64">
-        <v>-13.22657423392885</v>
+        <v>-13.75457618932719</v>
       </c>
       <c r="F64">
-        <v>0.2907542995450719</v>
+        <v>-0.203188530274295</v>
       </c>
       <c r="G64">
-        <v>-5.830189657696664</v>
+        <v>-6.274782681438627</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.79733822802412</v>
       </c>
       <c r="E65">
-        <v>-13.21587344984873</v>
+        <v>-13.93440189217178</v>
       </c>
       <c r="F65">
-        <v>0.1657017130501423</v>
+        <v>-0.3073480764797898</v>
       </c>
       <c r="G65">
-        <v>-5.904534578872077</v>
+        <v>-5.504418734450223</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.9900918853999</v>
       </c>
       <c r="E66">
-        <v>-13.31721164119237</v>
+        <v>-14.32600621045908</v>
       </c>
       <c r="F66">
-        <v>0.1478264243825773</v>
+        <v>0.161235662368603</v>
       </c>
       <c r="G66">
-        <v>-6.409760244165793</v>
+        <v>-5.831950867923557</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.17052759962731</v>
       </c>
       <c r="E67">
-        <v>-13.3557806543157</v>
+        <v>-14.3253088254619</v>
       </c>
       <c r="F67">
-        <v>0.06265947136799009</v>
+        <v>-0.1591575465602898</v>
       </c>
       <c r="G67">
-        <v>-6.824707332603582</v>
+        <v>-5.970867979842454</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.3298559005241</v>
       </c>
       <c r="E68">
-        <v>-13.73075641604684</v>
+        <v>-14.0424603389428</v>
       </c>
       <c r="F68">
-        <v>-0.3100815528898382</v>
+        <v>-0.3120390134013214</v>
       </c>
       <c r="G68">
-        <v>-6.165786280103663</v>
+        <v>-5.487703790022442</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.46934742730641</v>
       </c>
       <c r="E69">
-        <v>-13.060170928043</v>
+        <v>-12.98679153522271</v>
       </c>
       <c r="F69">
-        <v>-0.1352340850016615</v>
+        <v>-0.7202455479295008</v>
       </c>
       <c r="G69">
-        <v>-6.169576854746128</v>
+        <v>-5.539676044443461</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.59089594346207</v>
       </c>
       <c r="E70">
-        <v>-13.0019030529863</v>
+        <v>-13.38853963528719</v>
       </c>
       <c r="F70">
-        <v>-0.2272157245703846</v>
+        <v>-0.4716076784702961</v>
       </c>
       <c r="G70">
-        <v>-6.545542269459</v>
+        <v>-6.042432042764879</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.68289173061514</v>
       </c>
       <c r="E71">
-        <v>-13.49970008675347</v>
+        <v>-12.76284038164738</v>
       </c>
       <c r="F71">
-        <v>-0.36783059724338</v>
+        <v>-0.5137817669984486</v>
       </c>
       <c r="G71">
-        <v>-6.814169866152082</v>
+        <v>-6.595061409635418</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.75699713434548</v>
       </c>
       <c r="E72">
-        <v>-13.57360025408465</v>
+        <v>-13.02983468066561</v>
       </c>
       <c r="F72">
-        <v>-0.3900064393243208</v>
+        <v>-0.6179349783802816</v>
       </c>
       <c r="G72">
-        <v>-6.462225769872163</v>
+        <v>-6.555914208633537</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.79813738375779</v>
       </c>
       <c r="E73">
-        <v>-13.0537948366402</v>
+        <v>-13.80778575891731</v>
       </c>
       <c r="F73">
-        <v>-0.5584098078425745</v>
+        <v>-0.83151197443053</v>
       </c>
       <c r="G73">
-        <v>-6.425687278755226</v>
+        <v>-6.340437420573454</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.81907625153104</v>
       </c>
       <c r="E74">
-        <v>-12.97523939802914</v>
+        <v>-12.34871143364592</v>
       </c>
       <c r="F74">
-        <v>-0.5225151132691395</v>
+        <v>-1.186400673756567</v>
       </c>
       <c r="G74">
-        <v>-6.778574880513839</v>
+        <v>-6.808872993289248</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.80787131169879</v>
       </c>
       <c r="E75">
-        <v>-14.65719162853604</v>
+        <v>-13.89343278782438</v>
       </c>
       <c r="F75">
-        <v>-0.653368022679366</v>
+        <v>-0.9187385369881462</v>
       </c>
       <c r="G75">
-        <v>-6.243031239171478</v>
+        <v>-5.523659625124466</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.7752274951984</v>
       </c>
       <c r="E76">
-        <v>-14.11470308478717</v>
+        <v>-14.37544356120081</v>
       </c>
       <c r="F76">
-        <v>-0.464507924851381</v>
+        <v>-0.6501554752298971</v>
       </c>
       <c r="G76">
-        <v>-6.045103653015071</v>
+        <v>-6.653942772596896</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.72138535736518</v>
       </c>
       <c r="E77">
-        <v>-13.58427386732073</v>
+        <v>-14.01403057912265</v>
       </c>
       <c r="F77">
-        <v>-0.8780935165213505</v>
+        <v>-0.7853010195239224</v>
       </c>
       <c r="G77">
-        <v>-6.364945389200678</v>
+        <v>-5.695519975704651</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.64361904086851</v>
       </c>
       <c r="E78">
-        <v>-14.00745070638951</v>
+        <v>-15.66315590154795</v>
       </c>
       <c r="F78">
-        <v>-0.5751559141924312</v>
+        <v>-0.9039475155908995</v>
       </c>
       <c r="G78">
-        <v>-5.931472487925127</v>
+        <v>-6.197885329652436</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.55298466999778</v>
       </c>
       <c r="E79">
-        <v>-14.96982841707759</v>
+        <v>-15.66503068978712</v>
       </c>
       <c r="F79">
-        <v>-0.5742595366442925</v>
+        <v>-1.068409831938582</v>
       </c>
       <c r="G79">
-        <v>-5.883065691049904</v>
+        <v>-5.90720287857673</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-14.43841359470395</v>
       </c>
       <c r="E80">
-        <v>-16.21084766193163</v>
+        <v>-14.87726640836081</v>
       </c>
       <c r="F80">
-        <v>-0.7867255629948602</v>
+        <v>-1.016011338020352</v>
       </c>
       <c r="G80">
-        <v>-5.470051961207048</v>
+        <v>-5.825895880132229</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-14.31430579861973</v>
       </c>
       <c r="E81">
-        <v>-17.03178301546414</v>
+        <v>-16.63891978140271</v>
       </c>
       <c r="F81">
-        <v>-0.6585839581118659</v>
+        <v>-1.07186943751086</v>
       </c>
       <c r="G81">
-        <v>-5.514916474355251</v>
+        <v>-6.011567826702255</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-14.16775510797157</v>
       </c>
       <c r="E82">
-        <v>-17.03052862816401</v>
+        <v>-19.03378061798913</v>
       </c>
       <c r="F82">
-        <v>-1.061466073352338</v>
+        <v>-1.129375383006381</v>
       </c>
       <c r="G82">
-        <v>-5.780038203322245</v>
+        <v>-5.779740254223711</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.01083580247332</v>
       </c>
       <c r="E83">
-        <v>-16.85904437444155</v>
+        <v>-17.34701461961208</v>
       </c>
       <c r="F83">
-        <v>-0.8091833047287492</v>
+        <v>-1.28852594971368</v>
       </c>
       <c r="G83">
-        <v>-5.232487213308948</v>
+        <v>-5.269025704425884</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.83711911802071</v>
       </c>
       <c r="E84">
-        <v>-18.02695140644176</v>
+        <v>-18.56256572664699</v>
       </c>
       <c r="F84">
-        <v>-0.9397978663987022</v>
+        <v>-1.032297377801774</v>
       </c>
       <c r="G84">
-        <v>-5.377111705737549</v>
+        <v>-4.821367115514556</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.64919690583436</v>
       </c>
       <c r="E85">
-        <v>-19.1386147912667</v>
+        <v>-19.00634712245067</v>
       </c>
       <c r="F85">
-        <v>-1.110069216044217</v>
+        <v>-0.9697932564371253</v>
       </c>
       <c r="G85">
-        <v>-5.42938853034818</v>
+        <v>-5.576419789383832</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.45235815826834</v>
       </c>
       <c r="E86">
-        <v>-20.37723847337069</v>
+        <v>-20.43056578328502</v>
       </c>
       <c r="F86">
-        <v>-1.25630703656998</v>
+        <v>-1.229855188517353</v>
       </c>
       <c r="G86">
-        <v>-5.179366199585802</v>
+        <v>-5.280880768002014</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.23889868964146</v>
       </c>
       <c r="E87">
-        <v>-22.30689370362315</v>
+        <v>-21.83290738618831</v>
       </c>
       <c r="F87">
-        <v>-1.210653546145607</v>
+        <v>-1.223892535745723</v>
       </c>
       <c r="G87">
-        <v>-4.864159227155175</v>
+        <v>-4.702846274663107</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.02203067137595</v>
       </c>
       <c r="E88">
-        <v>-22.49412798994429</v>
+        <v>-22.89037399408945</v>
       </c>
       <c r="F88">
-        <v>-1.234234135373542</v>
+        <v>-1.255648214909157</v>
       </c>
       <c r="G88">
-        <v>-4.272157542186084</v>
+        <v>-4.155848145754868</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.79075265715344</v>
       </c>
       <c r="E89">
-        <v>-24.26229783708323</v>
+        <v>-25.11897643595828</v>
       </c>
       <c r="F89">
-        <v>-1.053569715657957</v>
+        <v>-1.338004089923839</v>
       </c>
       <c r="G89">
-        <v>-4.972619320112777</v>
+        <v>-4.7225042940753</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.55855325570475</v>
       </c>
       <c r="E90">
-        <v>-26.21688231674792</v>
+        <v>-27.07917622339248</v>
       </c>
       <c r="F90">
-        <v>-1.100804536438896</v>
+        <v>-0.601431179035487</v>
       </c>
       <c r="G90">
-        <v>-5.093722386484857</v>
+        <v>-4.270171214862521</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.31502853647325</v>
       </c>
       <c r="E91">
-        <v>-27.79088931233398</v>
+        <v>-29.16671217144836</v>
       </c>
       <c r="F91">
-        <v>-1.307336416724312</v>
+        <v>-0.8997997897983635</v>
       </c>
       <c r="G91">
-        <v>-5.025561564376802</v>
+        <v>-3.790982990235173</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.06674151407543</v>
       </c>
       <c r="E92">
-        <v>-29.47606355209734</v>
+        <v>-29.71210799551015</v>
       </c>
       <c r="F92">
-        <v>-1.121254930924966</v>
+        <v>-1.196944987741563</v>
       </c>
       <c r="G92">
-        <v>-4.88085099776418</v>
+        <v>-4.924692552340749</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.81074937570492</v>
       </c>
       <c r="E93">
-        <v>-30.79593937908395</v>
+        <v>-31.54820948123815</v>
       </c>
       <c r="F93">
-        <v>-1.527816786859961</v>
+        <v>-1.268674987916604</v>
       </c>
       <c r="G93">
-        <v>-4.461113549931065</v>
+        <v>-4.728824125509769</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.53847518195661</v>
       </c>
       <c r="E94">
-        <v>-33.73798705120221</v>
+        <v>-33.79846482157465</v>
       </c>
       <c r="F94">
-        <v>-1.464873187103778</v>
+        <v>-0.763982754196192</v>
       </c>
       <c r="G94">
-        <v>-4.96952064948802</v>
+        <v>-5.349405750119389</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.25510161777681</v>
       </c>
       <c r="E95">
-        <v>-35.75995748833804</v>
+        <v>-36.29942780416079</v>
       </c>
       <c r="F95">
-        <v>-1.338300242930026</v>
+        <v>-0.8632407305934016</v>
       </c>
       <c r="G95">
-        <v>-4.392810374364822</v>
+        <v>-4.497046211214315</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.94597226805967</v>
       </c>
       <c r="E96">
-        <v>-38.51069524752825</v>
+        <v>-39.00727638602437</v>
       </c>
       <c r="F96">
-        <v>-1.445875050942166</v>
+        <v>-0.6292774801466589</v>
       </c>
       <c r="G96">
-        <v>-4.68943525468352</v>
+        <v>-5.250463475587191</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.62315577080761</v>
       </c>
       <c r="E97">
-        <v>-40.15600533060209</v>
+        <v>-39.99221721845566</v>
       </c>
       <c r="F97">
-        <v>-1.307847953734999</v>
+        <v>-1.170141556975708</v>
       </c>
       <c r="G97">
-        <v>-5.55712261943542</v>
+        <v>-5.541109510661965</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.27324985108475</v>
       </c>
       <c r="E98">
-        <v>-43.11061725385463</v>
+        <v>-41.97829949908071</v>
       </c>
       <c r="F98">
-        <v>-1.808230131806543</v>
+        <v>-1.193947032443636</v>
       </c>
       <c r="G98">
-        <v>-5.67540841155358</v>
+        <v>-5.105411922784024</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.917111717543497</v>
       </c>
       <c r="E99">
-        <v>-44.92425977274159</v>
+        <v>-45.01358392254289</v>
       </c>
       <c r="F99">
-        <v>-1.777533951900538</v>
+        <v>-1.047710003770831</v>
       </c>
       <c r="G99">
-        <v>-6.126847643470756</v>
+        <v>-5.167944817475317</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.550291598431498</v>
       </c>
       <c r="E100">
-        <v>-47.74057889251089</v>
+        <v>-46.55669087573761</v>
       </c>
       <c r="F100">
-        <v>-1.595912181959069</v>
+        <v>-1.188424649916499</v>
       </c>
       <c r="G100">
-        <v>-5.455545150653962</v>
+        <v>-6.038019085561031</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.201666759564187</v>
       </c>
       <c r="E101">
-        <v>-49.557264545931</v>
+        <v>-50.51747651392491</v>
       </c>
       <c r="F101">
-        <v>-1.69321111413888</v>
+        <v>-1.214949348441236</v>
       </c>
       <c r="G101">
-        <v>-5.221542549756117</v>
+        <v>-5.155553445521825</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.865258543383431</v>
       </c>
       <c r="E102">
-        <v>-51.43757752339589</v>
+        <v>-51.96204726906824</v>
       </c>
       <c r="F102">
-        <v>-1.744482801298274</v>
+        <v>-1.176935655352943</v>
       </c>
       <c r="G102">
-        <v>-6.378243850631931</v>
+        <v>-5.711056365920451</v>
       </c>
     </row>
   </sheetData>
